--- a/Dataset/IT/xlsx/ITAMed_2022.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2022.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Oncologia</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Gastroenterologia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Gastroenterologia</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Oncologia; Cardiologia e Cardiochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia; Oncologia</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Nefrologia; Cardiologia e Cardiochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia; Nefrologia</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Immunologia e Reumatologia; Nefrologia</t>
+          <t>Immunologia e Reumatologia</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Endocrinologia; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Endocrinologia</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Genetica Medica</t>
+          <t>Neurologia e Neurochirurgia; Pediatria</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Pediatria; Chirurgia Generale</t>
+          <t>Chirurgia Generale; Pediatria</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Nefrologia; Genetica Medica</t>
+          <t>Nefrologia</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Oncologia</t>
+          <t>Chirurgia Generale</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Pediatria</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Neurologia e Neurochirurgia</t>
+          <t>Ortopedia e Traumatologia; Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Chirurgia Generale</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Ematologia; Oncologia</t>
+          <t>Ematologia</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Immunologia e Reumatologia</t>
+          <t>Malattie Infettive</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Nutrizione Clinica</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Chirurgia Generale</t>
+          <t>Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Medicina Legale</t>
+          <t>Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Oncologia; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Oncologia</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Immunologia e Reumatologia</t>
+          <t>Anestesia e Rianimazione; Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Otorinolaringoiatria; Anestesia e Rianimazione</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Oncologia; Genetica Medica</t>
+          <t>Genetica Medica; Oncologia</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Cardiologia e Cardiochirurgia</t>
+          <t>Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Igiene, Epidemiologia e Statistica; Malattie Infettive</t>
+          <t>Malattie Infettive; Igiene, Epidemiologia e Statistica</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Igiene, Epidemiologia e Statistica; Malattie Infettive</t>
+          <t>Malattie Infettive; Igiene, Epidemiologia e Statistica</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Medicina del Lavoro; Pneumologia e Chirurgia Toracica</t>
+          <t>Medicina del Lavoro</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">

--- a/Dataset/IT/xlsx/ITAMed_2022.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2022.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Immagine</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>

--- a/Dataset/IT/xlsx/ITAMed_2022.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2022.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="31.20703125" bestFit="1" customWidth="1" min="13" max="13"/>
@@ -476,15 +476,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>Tipo Domanda</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Immagine</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Categoria Immagine</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Percorso Immagine</t>
         </is>
@@ -547,6 +552,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -605,6 +615,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -663,6 +678,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -721,6 +741,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -779,6 +804,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -837,6 +867,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -895,6 +930,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -953,6 +993,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1011,6 +1056,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1069,6 +1119,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1127,6 +1182,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1185,6 +1245,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1245,10 +1310,15 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>images/2022/ssm2022153.png</t>
         </is>
@@ -1311,6 +1381,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1369,6 +1444,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1427,6 +1507,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1485,6 +1570,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1543,6 +1633,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1601,6 +1696,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1659,6 +1759,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1717,6 +1822,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1775,6 +1885,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1833,6 +1948,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1891,6 +2011,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1949,6 +2074,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2007,6 +2137,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2065,6 +2200,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2123,6 +2263,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2181,6 +2326,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2239,6 +2389,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2297,6 +2452,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2355,6 +2515,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2413,6 +2578,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2471,6 +2641,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2529,6 +2704,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2587,6 +2767,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2645,6 +2830,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2703,6 +2893,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2761,6 +2956,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2819,6 +3019,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2877,6 +3082,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2935,6 +3145,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2993,6 +3208,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3051,6 +3271,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3109,6 +3334,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3167,6 +3397,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3225,6 +3460,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3283,6 +3523,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3341,6 +3586,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3399,6 +3649,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3457,6 +3712,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3515,6 +3775,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3573,6 +3838,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3631,6 +3901,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3689,6 +3964,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3747,6 +4027,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3805,6 +4090,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3863,6 +4153,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3921,6 +4216,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3979,6 +4279,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4037,6 +4342,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4095,6 +4405,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4153,6 +4468,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4211,6 +4531,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4269,6 +4594,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4327,6 +4657,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4385,6 +4720,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4443,6 +4783,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4501,6 +4846,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4559,6 +4909,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4617,6 +4972,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4675,6 +5035,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4733,6 +5098,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4791,6 +5161,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4849,6 +5224,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4907,6 +5287,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4965,6 +5350,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5023,6 +5413,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5081,6 +5476,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5139,6 +5539,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5197,6 +5602,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5255,6 +5665,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5315,10 +5730,15 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
           <t>Upper limb X-ray</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>images/2022/ssm2022223.png</t>
         </is>
@@ -5383,10 +5803,15 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
           <t>Upper limb X-ray</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>images/2022/ssm2022224.png</t>
         </is>
@@ -5451,10 +5876,15 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
           <t>Knee arthroscopy image and knee MRI</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>images/2022/ssm2022225.png</t>
         </is>
@@ -5517,6 +5947,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5575,6 +6010,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5633,6 +6073,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5691,6 +6136,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5749,6 +6199,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5807,6 +6262,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5865,6 +6325,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5923,6 +6388,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5981,6 +6451,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6039,6 +6514,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6097,6 +6577,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6155,6 +6640,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6213,6 +6703,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6271,6 +6766,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6329,6 +6829,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6387,6 +6892,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6445,6 +6955,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6503,6 +7018,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6561,6 +7081,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6619,6 +7144,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6677,6 +7207,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6735,6 +7270,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6793,6 +7333,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6851,6 +7396,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6909,6 +7459,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6967,6 +7522,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7025,6 +7585,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7083,6 +7648,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7141,6 +7711,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7199,6 +7774,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7257,6 +7837,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7315,6 +7900,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7373,6 +7963,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7431,6 +8026,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7489,6 +8089,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7547,6 +8152,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7605,6 +8215,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7663,6 +8278,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7721,6 +8341,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7779,6 +8404,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7837,6 +8467,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7895,6 +8530,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7953,6 +8593,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8011,6 +8656,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8069,6 +8719,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8127,6 +8782,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8185,6 +8845,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8243,6 +8908,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8301,6 +8971,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8359,6 +9034,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8417,6 +9097,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8475,6 +9160,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8533,6 +9223,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8591,6 +9286,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8647,6 +9347,11 @@
       <c r="L141" t="inlineStr">
         <is>
           <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
